--- a/ValueSet-HIV.C.DE99.xlsx
+++ b/ValueSet-HIV.C.DE99.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T11:09:56+00:00</t>
+    <t>2026-10-14T17:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
